--- a/output/ARKK/00_Starter_Residual_5_to_7.5pct/ARKK_starter_residual_analysis.xlsx
+++ b/output/ARKK/00_Starter_Residual_5_to_7.5pct/ARKK_starter_residual_analysis.xlsx
@@ -552,13 +552,13 @@
         <v>90.79754601226993</v>
       </c>
       <c r="M2" t="n">
-        <v>108.0552147239264</v>
+        <v>110.4846625766871</v>
       </c>
       <c r="N2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O2" t="n">
-        <v>510.2027027027027</v>
+        <v>558.28</v>
       </c>
     </row>
   </sheetData>
@@ -572,52 +572,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bloomberg Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Entry Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Entry Weight %</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Max Weight Achieved %</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Final Weight %</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Days to Outcome</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Days as Small Position</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1129,7 +1086,7 @@
         <v>11.94915786517672</v>
       </c>
       <c r="G15" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1162,7 +1119,7 @@
         <v>11.94915786517672</v>
       </c>
       <c r="G16" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1195,7 +1152,7 @@
         <v>11.94915786517672</v>
       </c>
       <c r="G17" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1228,7 +1185,7 @@
         <v>11.94915786517672</v>
       </c>
       <c r="G18" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1261,7 +1218,7 @@
         <v>11.94915786517672</v>
       </c>
       <c r="G19" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1294,7 +1251,7 @@
         <v>10.82128288662342</v>
       </c>
       <c r="G20" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1327,7 +1284,7 @@
         <v>10.82128288662342</v>
       </c>
       <c r="G21" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1360,7 +1317,7 @@
         <v>9.754941219319619</v>
       </c>
       <c r="G22" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1393,7 +1350,7 @@
         <v>9.754941219319619</v>
       </c>
       <c r="G23" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1426,7 +1383,7 @@
         <v>9.754941219319619</v>
       </c>
       <c r="G24" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1459,7 +1416,7 @@
         <v>9.754941219319619</v>
       </c>
       <c r="G25" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1492,7 +1449,7 @@
         <v>9.754941219319619</v>
       </c>
       <c r="G26" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1525,7 +1482,7 @@
         <v>9.754941219319619</v>
       </c>
       <c r="G27" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1558,7 +1515,7 @@
         <v>7.346860535663459</v>
       </c>
       <c r="G28" t="n">
-        <v>6.121763294974695</v>
+        <v>6.436808994976079</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1566,7 +1523,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29">
@@ -1591,7 +1548,7 @@
         <v>7.48913444722479</v>
       </c>
       <c r="G29" t="n">
-        <v>3.011860975600977</v>
+        <v>2.943761256716523</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1599,7 +1556,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>65</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30">
@@ -1624,7 +1581,7 @@
         <v>10.13324399523147</v>
       </c>
       <c r="G30" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1657,7 +1614,7 @@
         <v>7.543561965908506</v>
       </c>
       <c r="G31" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1690,7 +1647,7 @@
         <v>7.433296119579122</v>
       </c>
       <c r="G32" t="n">
-        <v>1.07193712212154</v>
+        <v>1.158512882497985</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1698,7 +1655,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>926</v>
+        <v>970</v>
       </c>
     </row>
     <row r="33">
@@ -1921,7 +1878,7 @@
         <v>8.525601764038635</v>
       </c>
       <c r="G39" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1954,7 +1911,7 @@
         <v>8.525601764038635</v>
       </c>
       <c r="G40" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1987,7 +1944,7 @@
         <v>8.525601764038635</v>
       </c>
       <c r="G41" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2020,7 +1977,7 @@
         <v>8.525601764038635</v>
       </c>
       <c r="G42" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2053,7 +2010,7 @@
         <v>8.525601764038635</v>
       </c>
       <c r="G43" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2086,7 +2043,7 @@
         <v>8.477002814113927</v>
       </c>
       <c r="G44" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2119,7 +2076,7 @@
         <v>8.477002814113927</v>
       </c>
       <c r="G45" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2152,7 +2109,7 @@
         <v>8.477002814113927</v>
       </c>
       <c r="G46" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2185,7 +2142,7 @@
         <v>8.477002814113927</v>
       </c>
       <c r="G47" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2218,7 +2175,7 @@
         <v>7.290329191037831</v>
       </c>
       <c r="G48" t="n">
-        <v>1.283164029797741</v>
+        <v>1.050630193051837</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2226,7 +2183,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1969</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="49">
@@ -2251,7 +2208,7 @@
         <v>7.35607676793861</v>
       </c>
       <c r="G49" t="n">
-        <v>1.231609818750312</v>
+        <v>2.104449930396637</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2259,7 +2216,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2533</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="50">
@@ -2614,7 +2571,7 @@
         <v>8.274118065635113</v>
       </c>
       <c r="G60" t="n">
-        <v>4.267231954982065</v>
+        <v>4.123307476930346</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2647,7 +2604,7 @@
         <v>6.619670546506724</v>
       </c>
       <c r="G61" t="n">
-        <v>4.267231954982065</v>
+        <v>4.123307476930346</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2655,7 +2612,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>112</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62">
@@ -2680,7 +2637,7 @@
         <v>8.337791569994524</v>
       </c>
       <c r="G62" t="n">
-        <v>5.548733388209437</v>
+        <v>4.654967477232781</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2713,7 +2670,7 @@
         <v>8.337791569994524</v>
       </c>
       <c r="G63" t="n">
-        <v>5.548733388209437</v>
+        <v>4.654967477232781</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2746,7 +2703,7 @@
         <v>8.337791569994524</v>
       </c>
       <c r="G64" t="n">
-        <v>5.548733388209437</v>
+        <v>4.654967477232781</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2779,7 +2736,7 @@
         <v>7.523891839558392</v>
       </c>
       <c r="G65" t="n">
-        <v>5.548733388209437</v>
+        <v>4.654967477232781</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2812,7 +2769,7 @@
         <v>7.301605478808823</v>
       </c>
       <c r="G66" t="n">
-        <v>5.548733388209437</v>
+        <v>4.654967477232781</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2820,7 +2777,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>68</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67">
@@ -2845,7 +2802,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G67" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2878,7 +2835,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G68" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2911,7 +2868,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G69" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2944,7 +2901,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G70" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2977,7 +2934,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G71" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3010,7 +2967,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G72" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3043,7 +3000,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G73" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3076,7 +3033,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G74" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3109,7 +3066,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G75" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3142,7 +3099,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G76" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3175,7 +3132,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G77" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3208,7 +3165,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G78" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3241,7 +3198,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G79" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3274,7 +3231,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G80" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3307,7 +3264,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G81" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3340,7 +3297,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G82" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3373,7 +3330,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G83" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3406,7 +3363,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G84" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3439,7 +3396,7 @@
         <v>11.37479646261744</v>
       </c>
       <c r="G85" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3472,7 +3429,7 @@
         <v>7.86444179164615</v>
       </c>
       <c r="G86" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3505,7 +3462,7 @@
         <v>7.86444179164615</v>
       </c>
       <c r="G87" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3538,7 +3495,7 @@
         <v>7.86444179164615</v>
       </c>
       <c r="G88" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -3571,7 +3528,7 @@
         <v>7.86444179164615</v>
       </c>
       <c r="G89" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3604,7 +3561,7 @@
         <v>7.86444179164615</v>
       </c>
       <c r="G90" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3637,7 +3594,7 @@
         <v>7.86444179164615</v>
       </c>
       <c r="G91" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -3670,7 +3627,7 @@
         <v>7.66995448935486</v>
       </c>
       <c r="G92" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3703,7 +3660,7 @@
         <v>7.572380499239066</v>
       </c>
       <c r="G93" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3736,7 +3693,7 @@
         <v>7.569138656185524</v>
       </c>
       <c r="G94" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3769,7 +3726,7 @@
         <v>7.343061860723775</v>
       </c>
       <c r="G95" t="n">
-        <v>6.859793191005789</v>
+        <v>5.195425181213173</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -3777,7 +3734,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="96">
@@ -4495,7 +4452,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G117" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4528,7 +4485,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G118" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -4561,7 +4518,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G119" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -4594,7 +4551,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G120" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -4627,7 +4584,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G121" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -4660,7 +4617,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G122" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -4693,7 +4650,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G123" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -4726,7 +4683,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G124" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -4759,7 +4716,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G125" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -4792,7 +4749,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G126" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -4825,7 +4782,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G127" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -4858,7 +4815,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G128" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -4891,7 +4848,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G129" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -4924,7 +4881,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G130" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -4957,7 +4914,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G131" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -4990,7 +4947,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G132" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -5023,7 +4980,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G133" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -5056,7 +5013,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G134" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -5089,7 +5046,7 @@
         <v>25.15214959020717</v>
       </c>
       <c r="G135" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5122,7 +5079,7 @@
         <v>17.20645145100504</v>
       </c>
       <c r="G136" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -5155,7 +5112,7 @@
         <v>17.20645145100504</v>
       </c>
       <c r="G137" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -5188,7 +5145,7 @@
         <v>17.20645145100504</v>
       </c>
       <c r="G138" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -5221,7 +5178,7 @@
         <v>17.20645145100504</v>
       </c>
       <c r="G139" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -5254,7 +5211,7 @@
         <v>17.20645145100504</v>
       </c>
       <c r="G140" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -5287,7 +5244,7 @@
         <v>17.20645145100504</v>
       </c>
       <c r="G141" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -5320,7 +5277,7 @@
         <v>17.20645145100504</v>
       </c>
       <c r="G142" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -5353,7 +5310,7 @@
         <v>17.20645145100504</v>
       </c>
       <c r="G143" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -5386,7 +5343,7 @@
         <v>17.20645145100504</v>
       </c>
       <c r="G144" t="n">
-        <v>11.05528643740157</v>
+        <v>11.47535602817966</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -5419,7 +5376,7 @@
         <v>8.981169534111476</v>
       </c>
       <c r="G145" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -5452,7 +5409,7 @@
         <v>8.981169534111476</v>
       </c>
       <c r="G146" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -5485,7 +5442,7 @@
         <v>8.981169534111476</v>
       </c>
       <c r="G147" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -5518,7 +5475,7 @@
         <v>8.981169534111476</v>
       </c>
       <c r="G148" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -5551,7 +5508,7 @@
         <v>8.981169534111476</v>
       </c>
       <c r="G149" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -5584,7 +5541,7 @@
         <v>8.981169534111476</v>
       </c>
       <c r="G150" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -5617,7 +5574,7 @@
         <v>8.981169534111476</v>
       </c>
       <c r="G151" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -5650,7 +5607,7 @@
         <v>8.981169534111476</v>
       </c>
       <c r="G152" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -5683,7 +5640,7 @@
         <v>8.981169534111476</v>
       </c>
       <c r="G153" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -5716,7 +5673,7 @@
         <v>7.437403731456977</v>
       </c>
       <c r="G154" t="n">
-        <v>1.232373234572589</v>
+        <v>1.060020615169871</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -5724,7 +5681,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1846</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="155">
@@ -6068,7 +6025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6424,381 +6381,381 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BIDU US Equity</t>
+          <t>BABA US Equity</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>43690</v>
+        <v>43363</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>44176</v>
+        <v>45925</v>
       </c>
       <c r="D19" t="n">
-        <v>486</v>
+        <v>2562</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1774855932996128</v>
+        <v>0.1555838802032586</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CRSP US Equity</t>
+          <t>BIDU US Equity</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>43220</v>
+        <v>43690</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>43252</v>
+        <v>44176</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>486</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2671023170990939</v>
+        <v>0.1774855932996128</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DDD US Equity</t>
+          <t>BIDU US Equity</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>42794</v>
+        <v>44334</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>44512</v>
+        <v>45925</v>
       </c>
       <c r="D21" t="n">
-        <v>1718</v>
+        <v>1591</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2516488494639003</v>
+        <v>0.1536917164820487</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EXAS US Equity</t>
+          <t>CRSP US Equity</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45475</v>
+        <v>43220</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>45877</v>
+        <v>43252</v>
       </c>
       <c r="D22" t="n">
-        <v>402</v>
+        <v>32</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8467072203452185</v>
+        <v>0.2671023170990939</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FANUY US Equity</t>
+          <t>DDD US Equity</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>42398</v>
+        <v>42794</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>42948</v>
+        <v>44512</v>
       </c>
       <c r="D23" t="n">
-        <v>550</v>
+        <v>1718</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4875444081657636</v>
+        <v>0.2516488494639003</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GM US Equity</t>
+          <t>EXAS US Equity</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>42829</v>
+        <v>45475</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>43033</v>
+        <v>45877</v>
       </c>
       <c r="D24" t="n">
-        <v>204</v>
+        <v>402</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4913143939062111</v>
+        <v>0.8467072203452185</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GOOG US Equity</t>
+          <t>FANUY US Equity</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>42142</v>
+        <v>42398</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>42458</v>
+        <v>42948</v>
       </c>
       <c r="D25" t="n">
-        <v>316</v>
+        <v>550</v>
       </c>
       <c r="E25" t="n">
-        <v>1.968287853227933</v>
+        <v>0.4875444081657636</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ICE US Equity</t>
+          <t>GM US Equity</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>43427</v>
+        <v>42829</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>44062</v>
+        <v>43033</v>
       </c>
       <c r="D26" t="n">
-        <v>635</v>
+        <v>204</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4197300085576299</v>
+        <v>0.4913143939062111</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ILMN US Equity</t>
+          <t>GOOG US Equity</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>44140</v>
+        <v>42142</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>45600</v>
+        <v>42458</v>
       </c>
       <c r="D27" t="n">
-        <v>1460</v>
+        <v>316</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1631762599743918</v>
+        <v>1.968287853227933</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>INTU US Equity</t>
+          <t>ICE US Equity</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>42199</v>
+        <v>43427</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>42915</v>
+        <v>44062</v>
       </c>
       <c r="D28" t="n">
-        <v>716</v>
+        <v>635</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4960517874846671</v>
+        <v>0.4197300085576299</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IOVA US Equity</t>
+          <t>ILMN US Equity</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>43909</v>
+        <v>44140</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>43983</v>
+        <v>45600</v>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>1460</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4817989418673881</v>
+        <v>0.1631762599743918</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IRDM US Equity</t>
+          <t>INTU US Equity</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>44610</v>
+        <v>42199</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>45700</v>
+        <v>42915</v>
       </c>
       <c r="D30" t="n">
-        <v>1090</v>
+        <v>716</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2451590244595243</v>
+        <v>0.4960517874846671</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LC US Equity</t>
+          <t>IOVA US Equity</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>42108</v>
+        <v>43909</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>42373</v>
+        <v>43983</v>
       </c>
       <c r="D31" t="n">
-        <v>265</v>
+        <v>74</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2484844303043602</v>
+        <v>0.4817989418673881</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LC US Equity</t>
+          <t>IRDM US Equity</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>42389</v>
+        <v>44610</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>42510</v>
+        <v>45700</v>
       </c>
       <c r="D32" t="n">
-        <v>121</v>
+        <v>1090</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4798186261651735</v>
+        <v>0.2451590244595243</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MBBYF US Equity</t>
+          <t>LC US Equity</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>42041</v>
+        <v>42108</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>42312</v>
+        <v>42373</v>
       </c>
       <c r="D33" t="n">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2530496535245101</v>
+        <v>0.2484844303043602</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MDSO US Equity</t>
+          <t>LC US Equity</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>42458</v>
+        <v>42389</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>42836</v>
+        <v>42510</v>
       </c>
       <c r="D34" t="n">
-        <v>378</v>
+        <v>121</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4980202279847413</v>
+        <v>0.4798186261651735</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MELI US Equity</t>
+          <t>MBBYF US Equity</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>42402</v>
+        <v>42041</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>43250</v>
+        <v>42312</v>
       </c>
       <c r="D35" t="n">
-        <v>848</v>
+        <v>271</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5014902113002812</v>
+        <v>0.2530496535245101</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MELI US Equity</t>
+          <t>MDSO US Equity</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>43389</v>
+        <v>42458</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>43720</v>
+        <v>42836</v>
       </c>
       <c r="D36" t="n">
-        <v>331</v>
+        <v>378</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5042868338863414</v>
+        <v>0.4980202279847413</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>META US Equity</t>
+          <t>MELI US Equity</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>43277</v>
+        <v>42402</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>43633</v>
+        <v>43250</v>
       </c>
       <c r="D37" t="n">
-        <v>356</v>
+        <v>848</v>
       </c>
       <c r="E37" t="n">
-        <v>1.015456084431241</v>
+        <v>0.5014902113002812</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>META US Equity</t>
+          <t>MELI US Equity</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>43690</v>
+        <v>43389</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>44050</v>
+        <v>43720</v>
       </c>
       <c r="D38" t="n">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="E38" t="n">
-        <v>1.128319817305769</v>
+        <v>0.5042868338863414</v>
       </c>
     </row>
     <row r="39">
@@ -6808,662 +6765,662 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>44152</v>
+        <v>43277</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>45090</v>
+        <v>43633</v>
       </c>
       <c r="D39" t="n">
-        <v>938</v>
+        <v>356</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5117047168118555</v>
+        <v>1.015456084431241</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NTDOY US Equity</t>
+          <t>META US Equity</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>43217</v>
+        <v>43690</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>44064</v>
+        <v>44050</v>
       </c>
       <c r="D40" t="n">
-        <v>847</v>
+        <v>360</v>
       </c>
       <c r="E40" t="n">
-        <v>0.07378429246598177</v>
+        <v>1.128319817305769</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NVDA US Equity</t>
+          <t>META US Equity</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>43941</v>
+        <v>44152</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>44708</v>
+        <v>45090</v>
       </c>
       <c r="D41" t="n">
-        <v>767</v>
+        <v>938</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4049662906836736</v>
+        <v>0.5117047168118555</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NVDA US Equity</t>
+          <t>NTDOY US Equity</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>44937</v>
+        <v>43217</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>45755</v>
+        <v>44064</v>
       </c>
       <c r="D42" t="n">
-        <v>818</v>
+        <v>847</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3305475183913147</v>
+        <v>0.07378429246598177</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PACB US Equity</t>
+          <t>NVDA US Equity</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>42065</v>
+        <v>43941</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>43110</v>
+        <v>44708</v>
       </c>
       <c r="D43" t="n">
-        <v>1045</v>
+        <v>767</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4621782788964639</v>
+        <v>0.4049662906836736</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PACB US Equity</t>
+          <t>NVDA US Equity</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>43427</v>
+        <v>44937</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>44061</v>
+        <v>45755</v>
       </c>
       <c r="D44" t="n">
-        <v>634</v>
+        <v>818</v>
       </c>
       <c r="E44" t="n">
-        <v>0.003631100790811985</v>
+        <v>0.3305475183913147</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PINS US Equity</t>
+          <t>PACB US Equity</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>44271</v>
+        <v>42065</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>45278</v>
+        <v>43110</v>
       </c>
       <c r="D45" t="n">
-        <v>1007</v>
+        <v>1045</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1841894457298311</v>
+        <v>0.4621782788964639</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PLTR US Equity</t>
+          <t>PACB US Equity</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>44620</v>
+        <v>43427</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>45057</v>
+        <v>44061</v>
       </c>
       <c r="D46" t="n">
-        <v>437</v>
+        <v>634</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5108595090123392</v>
+        <v>0.003631100790811985</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PRLB US Equity</t>
+          <t>PINS US Equity</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>43277</v>
+        <v>44271</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>43508</v>
+        <v>45278</v>
       </c>
       <c r="D47" t="n">
-        <v>231</v>
+        <v>1007</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3038956856049196</v>
+        <v>0.1841894457298311</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PYPL US Equity</t>
+          <t>PLTR US Equity</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>43220</v>
+        <v>44620</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>43861</v>
+        <v>45057</v>
       </c>
       <c r="D48" t="n">
-        <v>641</v>
+        <v>437</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5054318209415705</v>
+        <v>0.5108595090123392</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PYPL US Equity</t>
+          <t>PRLB US Equity</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>43909</v>
+        <v>43277</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>44139</v>
+        <v>43508</v>
       </c>
       <c r="D49" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E49" t="n">
-        <v>1.011077438029077</v>
+        <v>0.3038956856049196</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QCOM US Equity</t>
+          <t>PYPL US Equity</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>42041</v>
+        <v>43220</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>42437</v>
+        <v>43861</v>
       </c>
       <c r="D50" t="n">
-        <v>396</v>
+        <v>641</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5063940383503459</v>
+        <v>0.5054318209415705</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QCOM US Equity</t>
+          <t>PYPL US Equity</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>42492</v>
+        <v>43909</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>42761</v>
+        <v>44139</v>
       </c>
       <c r="D51" t="n">
-        <v>269</v>
+        <v>230</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9564386412945145</v>
+        <v>1.011077438029077</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>REGN US Equity</t>
+          <t>QCOM US Equity</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>43718</v>
+        <v>42041</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>44208</v>
+        <v>42437</v>
       </c>
       <c r="D52" t="n">
-        <v>490</v>
+        <v>396</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1485730774152069</v>
+        <v>0.5063940383503459</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SCHW US Equity</t>
+          <t>QCOM US Equity</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>42004</v>
+        <v>42492</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>42510</v>
+        <v>42761</v>
       </c>
       <c r="D53" t="n">
-        <v>506</v>
+        <v>269</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5009728625923319</v>
+        <v>0.9564386412945145</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SE US Equity</t>
+          <t>REGN US Equity</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>43909</v>
+        <v>43718</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>44062</v>
+        <v>44208</v>
       </c>
       <c r="D54" t="n">
-        <v>153</v>
+        <v>490</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5073047995186792</v>
+        <v>0.1485730774152069</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SE US Equity</t>
+          <t>SCHW US Equity</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>44487</v>
+        <v>42004</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>44593</v>
+        <v>42510</v>
       </c>
       <c r="D55" t="n">
-        <v>106</v>
+        <v>506</v>
       </c>
       <c r="E55" t="n">
-        <v>0.02795461985489596</v>
+        <v>0.5009728625923319</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SNAP US Equity</t>
+          <t>SE US Equity</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>44035</v>
+        <v>44062</v>
       </c>
       <c r="D56" t="n">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="E56" t="n">
-        <v>0.4945624760246113</v>
+        <v>0.5073047995186792</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SNAP US Equity</t>
+          <t>SE US Equity</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>44077</v>
+        <v>44487</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>44235</v>
+        <v>44593</v>
       </c>
       <c r="D57" t="n">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5279001378718579</v>
+        <v>0.02795461985489596</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SPOT US Equity</t>
+          <t>SNAP US Equity</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>43718</v>
+        <v>43909</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>43978</v>
+        <v>44035</v>
       </c>
       <c r="D58" t="n">
-        <v>260</v>
+        <v>126</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4853398926368807</v>
+        <v>0.4945624760246113</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TCEHY US Equity</t>
+          <t>SNAP US Equity</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>43909</v>
+        <v>44077</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>44076</v>
+        <v>44235</v>
       </c>
       <c r="D59" t="n">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="E59" t="n">
-        <v>0.123539086270048</v>
+        <v>0.5279001378718579</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TDOC US Equity</t>
+          <t>SPOT US Equity</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>43909</v>
+        <v>43718</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>44049</v>
+        <v>43978</v>
       </c>
       <c r="D60" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9832553552772862</v>
+        <v>0.4853398926368807</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TER US Equity</t>
+          <t>TCEHY US Equity</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>44125</v>
+        <v>43909</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>44228</v>
+        <v>44076</v>
       </c>
       <c r="D61" t="n">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="E61" t="n">
-        <v>0.1473049641047281</v>
+        <v>0.123539086270048</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TER US Equity</t>
+          <t>TDOC US Equity</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>44474</v>
+        <v>43909</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>45090</v>
+        <v>44049</v>
       </c>
       <c r="D62" t="n">
-        <v>616</v>
+        <v>140</v>
       </c>
       <c r="E62" t="n">
-        <v>0.03768149071833461</v>
+        <v>0.9832553552772862</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TREE US Equity</t>
+          <t>TER US Equity</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>43193</v>
+        <v>44125</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>43312</v>
+        <v>44228</v>
       </c>
       <c r="D63" t="n">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="E63" t="n">
-        <v>1.050984313232082</v>
+        <v>0.1473049641047281</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TRMB US Equity</t>
+          <t>TER US Equity</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>42383</v>
+        <v>44474</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>44291</v>
+        <v>45090</v>
       </c>
       <c r="D64" t="n">
-        <v>1908</v>
+        <v>616</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1589357122174727</v>
+        <v>0.03768149071833461</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TSM US Equity</t>
+          <t>TREE US Equity</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>43397</v>
+        <v>43193</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>44021</v>
+        <v>43312</v>
       </c>
       <c r="D65" t="n">
-        <v>624</v>
+        <v>119</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3591561354308993</v>
+        <v>1.050984313232082</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TSM US Equity</t>
+          <t>TRMB US Equity</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>44313</v>
+        <v>42383</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>45797</v>
+        <v>44291</v>
       </c>
       <c r="D66" t="n">
-        <v>1484</v>
+        <v>1908</v>
       </c>
       <c r="E66" t="n">
-        <v>0.4103560491936882</v>
+        <v>0.1589357122174727</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TTD US Equity</t>
+          <t>TSM US Equity</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>43901</v>
+        <v>43397</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>45243</v>
+        <v>44021</v>
       </c>
       <c r="D67" t="n">
-        <v>1342</v>
+        <v>624</v>
       </c>
       <c r="E67" t="n">
-        <v>0.5068798618366805</v>
+        <v>0.3591561354308993</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TWLO US Equity</t>
+          <t>TSM US Equity</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>43040</v>
+        <v>44313</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>44021</v>
+        <v>45797</v>
       </c>
       <c r="D68" t="n">
-        <v>981</v>
+        <v>1484</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4945969629745466</v>
+        <v>0.4103560491936882</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TWOUQ US Equity</t>
+          <t>TTD US Equity</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>43217</v>
+        <v>43901</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>43411</v>
+        <v>45243</v>
       </c>
       <c r="D69" t="n">
-        <v>194</v>
+        <v>1342</v>
       </c>
       <c r="E69" t="n">
-        <v>0.5237886032674073</v>
+        <v>0.5068798618366805</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TWTR US Equity</t>
+          <t>TWLO US Equity</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>42408</v>
+        <v>43040</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>42562</v>
+        <v>44021</v>
       </c>
       <c r="D70" t="n">
-        <v>154</v>
+        <v>981</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4892660769048036</v>
+        <v>0.4945969629745466</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TWTR US Equity</t>
+          <t>TWOUQ US Equity</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>43927</v>
+        <v>43217</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>44250</v>
+        <v>43411</v>
       </c>
       <c r="D71" t="n">
-        <v>323</v>
+        <v>194</v>
       </c>
       <c r="E71" t="n">
-        <v>0.276087329749161</v>
+        <v>0.5237886032674073</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>USD Curncy</t>
+          <t>TWTR US Equity</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>42004</v>
+        <v>42408</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>42041</v>
+        <v>42562</v>
       </c>
       <c r="D72" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>0.4892660769048036</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>XLNX US Equity</t>
+          <t>TWTR US Equity</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>42397</v>
+        <v>43927</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>42766</v>
+        <v>44250</v>
       </c>
       <c r="D73" t="n">
-        <v>369</v>
+        <v>323</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9656078142539634</v>
+        <v>0.276087329749161</v>
       </c>
     </row>
     <row r="74">
@@ -7473,34 +7430,53 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>43389</v>
+        <v>42397</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>43581</v>
+        <v>42766</v>
       </c>
       <c r="D74" t="n">
-        <v>192</v>
+        <v>369</v>
       </c>
       <c r="E74" t="n">
-        <v>0.4992442592796971</v>
+        <v>0.9656078142539634</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>XLNX US Equity</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>43389</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>43581</v>
+      </c>
+      <c r="D75" t="n">
+        <v>192</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.4992442592796971</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>Z US Equity</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n">
+      <c r="B76" s="2" t="n">
         <v>42375</v>
       </c>
-      <c r="C75" s="2" t="n">
+      <c r="C76" s="2" t="n">
         <v>43320</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D76" t="n">
         <v>945</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E76" t="n">
         <v>1.22404643619271</v>
       </c>
     </row>
